--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -83,67 +83,46 @@
     <t>Prefabs/UI/Notice/UINotice.prefab</t>
   </si>
   <si>
+    <t>Prefabs/UI/Guide/UIGuide.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/Effect/UIEffect.prefab</t>
+  </si>
+  <si>
     <t>Prefabs/UI/Setting/UISetting.prefab</t>
   </si>
   <si>
+    <t>Prefabs/UI/UserLevel/UIUserLevel.prefab</t>
+  </si>
+  <si>
     <t>Prefabs/UI/ReStart/UIReStart.prefab</t>
   </si>
   <si>
+    <t>Prefabs/UI/LevelCompleted/UILevelCompleted.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/LevelFailure/UILevelFailure.prefab</t>
+  </si>
+  <si>
     <t>Prefabs/UI/Prop/UIProp.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/WithdrawGoal/UIWithdrawGoal.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawHistory/UIWithdrawHistory.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawInformation/UIWithdrawInformation.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawPayment/UIWithdrawPayment.prefab</t>
+    <t>Prefabs/UI/WithdrawEnterInfo/UIWithdrawEnterInfo.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawFeedback/UIWithdrawFeedback.prefab</t>
   </si>
   <si>
     <t>Prefabs/UI/WithdrawConfirm/UIWithdrawConfirm.prefab</t>
   </si>
   <si>
+    <t>Prefabs/UI/WithdrawRecords/UIWithdrawRecords.prefab</t>
+  </si>
+  <si>
     <t>Prefabs/UI/WithdrawProgress/UIWithdrawProgress.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/WithdrawKeepEarn/UIWithdrawKeepEarn.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawContinue/UIWithdrawContinue.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawTarget/UIWithdrawTarget.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/Effect/UIEffect.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/RewardMsg/UIRewardMsg.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/UserLevel/UIUserLevel.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/LevelFail/UILevelFail.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/LevelSuccess/UILevelSuccess.prefab</t>
-  </si>
-  <si>
     <t>Prefabs/UI/LuckyReward/UILuckyReward.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/LuckySpin/UILuckySpin.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/Guide/UIGuide.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/LuckyUser/UILuckyUser.prefab</t>
   </si>
 </sst>
 </file>
@@ -781,12 +760,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1108,7 +1090,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.45" customWidth="1"/>
@@ -1230,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -1244,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -1258,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -1314,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1328,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
         <v>24</v>
@@ -1358,7 +1340,7 @@
       <c r="D17">
         <v>4</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1370,9 +1352,9 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>4</v>
-      </c>
-      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1386,7 +1368,7 @@
       <c r="D19">
         <v>4</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1430,104 +1412,6 @@
       </c>
       <c r="E22" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5">
-      <c r="B23">
-        <v>18</v>
-      </c>
-      <c r="C23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24">
-        <v>19</v>
-      </c>
-      <c r="C24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5">
-      <c r="B25">
-        <v>20</v>
-      </c>
-      <c r="C25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5">
-      <c r="B26">
-        <v>21</v>
-      </c>
-      <c r="C26" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="E26" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27">
-        <v>22</v>
-      </c>
-      <c r="C27" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>5</v>
-      </c>
-      <c r="E27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28">
-        <v>23</v>
-      </c>
-      <c r="C28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>7</v>
-      </c>
-      <c r="E28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29">
-        <v>24</v>
-      </c>
-      <c r="C29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -74,37 +74,49 @@
     <t>ui路径</t>
   </si>
   <si>
+    <t>Prefabs/UI/Effect/UIEffect.prefab</t>
+  </si>
+  <si>
     <t>Prefabs/UI/GamePlay/UIGamePlay.prefab</t>
   </si>
   <si>
+    <t>Prefabs/UI/Guide/UIGuide.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/LevelCompleted/UILevelCompleted.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/LevelFailure/UILevelFailure.prefab</t>
+  </si>
+  <si>
     <t>Prefabs/UI/Loading/UILoading.prefab</t>
   </si>
   <si>
+    <t>Prefabs/UI/LuckyReward/UILuckyReward.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/LuckySpin/UILuckySpin.prefab</t>
+  </si>
+  <si>
     <t>Prefabs/UI/Notice/UINotice.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/Guide/UIGuide.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/Effect/UIEffect.prefab</t>
+    <t>Prefabs/UI/Prop/UIProp.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/ReStart/UIReStart.prefab</t>
   </si>
   <si>
     <t>Prefabs/UI/Setting/UISetting.prefab</t>
   </si>
   <si>
+    <t>Prefabs/UI/Task/UITask.prefab</t>
+  </si>
+  <si>
     <t>Prefabs/UI/UserLevel/UIUserLevel.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/ReStart/UIReStart.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/LevelCompleted/UILevelCompleted.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/LevelFailure/UILevelFailure.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/Prop/UIProp.prefab</t>
+    <t>Prefabs/UI/WithdrawConfirm/UIWithdrawConfirm.prefab</t>
   </si>
   <si>
     <t>Prefabs/UI/WithdrawEnterInfo/UIWithdrawEnterInfo.prefab</t>
@@ -113,16 +125,28 @@
     <t>Prefabs/UI/WithdrawFeedback/UIWithdrawFeedback.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/WithdrawConfirm/UIWithdrawConfirm.prefab</t>
+    <t>Prefabs/UI/WithdrawGoal/UIWithdrawGoal.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawLuckyPlayer/UIWithdrawLuckyPlayer.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawProgress/UIWithdrawProgress.prefab</t>
   </si>
   <si>
     <t>Prefabs/UI/WithdrawRecords/UIWithdrawRecords.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/WithdrawProgress/UIWithdrawProgress.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/LuckyReward/UILuckyReward.prefab</t>
+    <t>Prefabs/UI/Child1/UIChild1.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/Child2/UIChild2.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/Child3/UIChild3.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/Child4/UIChild4.prefab</t>
   </si>
 </sst>
 </file>
@@ -765,7 +789,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1090,7 +1114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.45" customWidth="1"/>
@@ -1177,27 +1201,27 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="B6">
+      <c r="B6" s="2">
         <v>1</v>
       </c>
-      <c r="C6" t="b">
+      <c r="C6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -1205,213 +1229,325 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="B8">
+      <c r="B8" s="2">
         <v>3</v>
       </c>
-      <c r="C8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" s="2">
+        <v>4</v>
+      </c>
+      <c r="C9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" s="2">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="2">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13" s="2">
         <v>8</v>
       </c>
-      <c r="E8" t="s">
+      <c r="C13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="2">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="2">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="2">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="2">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="2">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="2">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>4</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="2">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="2">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="2">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="2">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>7</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10">
-        <v>5</v>
-      </c>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>6</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="C24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="B12">
-        <v>7</v>
-      </c>
-      <c r="C12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="2">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="B14">
-        <v>9</v>
-      </c>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="C27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="2">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15">
-        <v>10</v>
-      </c>
-      <c r="C15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="C28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>4</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="B16">
-        <v>11</v>
-      </c>
-      <c r="C16" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="C29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>4</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17">
-        <v>12</v>
-      </c>
-      <c r="C17" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>4</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5">
-      <c r="B18">
-        <v>13</v>
-      </c>
-      <c r="C18" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
-      <c r="B19">
-        <v>14</v>
-      </c>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5">
-      <c r="B20">
-        <v>15</v>
-      </c>
-      <c r="C20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21">
-        <v>16</v>
-      </c>
-      <c r="C21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22">
-        <v>17</v>
-      </c>
-      <c r="C22" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22" t="s">
-        <v>31</v>
+      <c r="C30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -784,14 +784,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1280,7 +1277,7 @@
       <c r="D11" s="2">
         <v>2</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1406,7 +1403,7 @@
       <c r="D20" s="2">
         <v>4</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1420,7 +1417,7 @@
       <c r="D21" s="2">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1434,7 +1431,7 @@
       <c r="D22" s="2">
         <v>5</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1448,7 +1445,7 @@
       <c r="D23" s="2">
         <v>4</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1462,7 +1459,7 @@
       <c r="D24" s="2">
         <v>4</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>33</v>
       </c>
     </row>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>Prefabs/UI/WithdrawRecords/UIWithdrawRecords.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawContinue/UIWithdrawContinue.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawKeepEarn/UIWithdrawKeepEarn.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawTarget/UIWithdrawTarget.prefab</t>
   </si>
   <si>
     <t>Prefabs/UI/Child1/UIChild1.prefab</t>
@@ -1111,7 +1120,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.45" customWidth="1"/>
@@ -1501,7 +1510,7 @@
       <c r="D27" s="2">
         <v>4</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1515,7 +1524,7 @@
       <c r="D28" s="2">
         <v>4</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1529,7 +1538,7 @@
       <c r="D29" s="2">
         <v>4</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1545,6 +1554,48 @@
       </c>
       <c r="E30" s="2" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="2">
+        <v>26</v>
+      </c>
+      <c r="C31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="2">
+        <v>27</v>
+      </c>
+      <c r="C32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="2">
+        <v>28</v>
+      </c>
+      <c r="C33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>4</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -146,16 +146,10 @@
     <t>Prefabs/UI/WithdrawTarget/UIWithdrawTarget.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/Child1/UIChild1.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/Child2/UIChild2.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/Child3/UIChild3.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/Child4/UIChild4.prefab</t>
+    <t>Prefabs/UI/NewGamePlay/UINewGamePlay.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/DateShow/UIDateShow.prefab</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="16.45" customWidth="1"/>
@@ -1552,7 +1546,7 @@
       <c r="D30" s="2">
         <v>4</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1566,37 +1560,33 @@
       <c r="D31" s="2">
         <v>4</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="2">
-        <v>27</v>
-      </c>
-      <c r="C32" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2">
-        <v>4</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="2">
-        <v>28</v>
-      </c>
-      <c r="C33" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2">
-        <v>4</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>Prefabs/UI/DateShow/UIDateShow.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawTip/UIWithdrawTip.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawGoal/UIWithdrawGoal2.prefab</t>
   </si>
 </sst>
 </file>
@@ -1565,16 +1571,32 @@
       </c>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="B32" s="2">
+        <v>27</v>
+      </c>
+      <c r="C32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="B33" s="2">
+        <v>28</v>
+      </c>
+      <c r="C33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>4</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="2"/>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -116,46 +116,13 @@
     <t>Prefabs/UI/UserLevel/UIUserLevel.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/WithdrawConfirm/UIWithdrawConfirm.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawEnterInfo/UIWithdrawEnterInfo.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawFeedback/UIWithdrawFeedback.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawGoal/UIWithdrawGoal.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawLuckyPlayer/UIWithdrawLuckyPlayer.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawProgress/UIWithdrawProgress.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawRecords/UIWithdrawRecords.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawContinue/UIWithdrawContinue.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawKeepEarn/UIWithdrawKeepEarn.prefab</t>
-  </si>
-  <si>
-    <t>Prefabs/UI/WithdrawTarget/UIWithdrawTarget.prefab</t>
-  </si>
-  <si>
     <t>Prefabs/UI/NewGamePlay/UINewGamePlay.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/DateShow/UIDateShow.prefab</t>
-  </si>
-  <si>
     <t>Prefabs/UI/WithdrawTip/UIWithdrawTip.prefab</t>
   </si>
   <si>
-    <t>Prefabs/UI/WithdrawGoal/UIWithdrawGoal2.prefab</t>
+    <t>Prefabs/UI/WithdrawGoal2/UIWithdrawGoal2.prefab</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1379,7 @@
       <c r="D20" s="2">
         <v>4</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1438,165 +1405,50 @@
         <v>0</v>
       </c>
       <c r="D22" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="2">
-        <v>18</v>
-      </c>
-      <c r="C23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2">
-        <v>4</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="2">
-        <v>19</v>
-      </c>
-      <c r="C24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2">
-        <v>4</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="2">
-        <v>20</v>
-      </c>
-      <c r="C25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2">
-        <v>4</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="2">
-        <v>21</v>
-      </c>
-      <c r="C26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2">
-        <v>4</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="2">
-        <v>22</v>
-      </c>
-      <c r="C27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2">
-        <v>4</v>
-      </c>
-      <c r="E27" t="s">
-        <v>36</v>
-      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="2">
-        <v>23</v>
-      </c>
-      <c r="C28" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2">
-        <v>4</v>
-      </c>
-      <c r="E28" t="s">
-        <v>37</v>
-      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="2">
-        <v>24</v>
-      </c>
-      <c r="C29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2">
-        <v>4</v>
-      </c>
-      <c r="E29" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="2">
-        <v>25</v>
-      </c>
-      <c r="C30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2">
-        <v>4</v>
-      </c>
-      <c r="E30" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="2">
-        <v>26</v>
-      </c>
-      <c r="C31" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2">
-        <v>4</v>
-      </c>
-      <c r="E31" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
-      <c r="B32" s="2">
-        <v>27</v>
-      </c>
-      <c r="C32" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2">
-        <v>4</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="2">
-        <v>28</v>
-      </c>
-      <c r="C33" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2">
-        <v>4</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="2"/>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>Prefabs/UI/WithdrawGoal2/UIWithdrawGoal2.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawAccount/UIWithdrawAccount.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawConfirm2/UIWithdrawConfirm2.prefab</t>
   </si>
 </sst>
 </file>
@@ -1412,16 +1418,32 @@
       </c>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="B23" s="2">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="B24" s="2">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>5</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="2"/>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ui配置|UIRes" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,15 @@
   </si>
   <si>
     <t>Prefabs/UI/WithdrawGoal2/UIWithdrawGoal2.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawAccount/UIWithdrawAccount.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/WithdrawConfirm2/UIWithdrawConfirm2.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/ProgressPanel/UIProgressPanel.prefab</t>
   </si>
 </sst>
 </file>
@@ -1412,22 +1421,46 @@
       </c>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="B23" s="2">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="B24" s="2">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>5</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="B25" s="2">
+        <v>20</v>
+      </c>
+      <c r="C25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="2"/>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,15 @@
   </si>
   <si>
     <t>Prefabs/UI/WithdrawGoal2/UIWithdrawGoal2.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/TotalReward/UITotalReward.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/TotalReward2/UITotalReward2.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/TotalReward3/UITotalReward3.prefab</t>
   </si>
 </sst>
 </file>
@@ -1412,22 +1421,46 @@
       </c>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="B23" s="2">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="B24" s="2">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="B25" s="2">
+        <v>20</v>
+      </c>
+      <c r="C25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2">
+        <v>3</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="2"/>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="ui配置|UIRes" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -132,6 +132,15 @@
   </si>
   <si>
     <t>Prefabs/UI/ProgressPanel/UIProgressPanel.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/TotalReward/UITotalReward.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/TotalReward2/UITotalReward2.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/TotalReward3/UITotalReward3.prefab</t>
   </si>
 </sst>
 </file>
@@ -1463,20 +1472,46 @@
       </c>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="B26" s="2">
+        <v>21</v>
+      </c>
+      <c r="C26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="B27" s="2">
+        <v>22</v>
+      </c>
+      <c r="C27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="2">
+        <v>23</v>
+      </c>
+      <c r="C28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="2"/>

--- a/DesignerConfigs/Datas/UIRes.xlsx
+++ b/DesignerConfigs/Datas/UIRes.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\_Project\AsWaterGameProj\DesignerConfigs\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ui配置|UIRes" sheetId="3" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -150,6 +155,12 @@
   </si>
   <si>
     <t>Prefabs/UI/DateShow/UIDateShow.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/UserAgreement/UIUserAgreementPanel.prefab</t>
+  </si>
+  <si>
+    <t>Prefabs/UI/PrivacyPolicy/UIPrivacyPolicyPanel.prefab</t>
   </si>
 </sst>
 </file>
@@ -1565,16 +1576,32 @@
       </c>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="B32" s="2">
+        <v>27</v>
+      </c>
+      <c r="C32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2">
+        <v>5</v>
+      </c>
+      <c r="E32" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="B33" s="2">
+        <v>28</v>
+      </c>
+      <c r="C33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="2"/>
